--- a/data/input/order_items/SMALL_TEST.xlsx
+++ b/data/input/order_items/SMALL_TEST.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\pyreview\PharmaSupplyBot\data\input\order_items\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39E4577B-E874-4FF3-8BBE-246DB52CBE7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3883EDC5-9C53-476D-B02F-72A468DA0927}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="43">
   <si>
     <t>كود</t>
   </si>
@@ -139,6 +139,21 @@
   </si>
   <si>
     <t>GINKGO BILOBA  30 CAP</t>
+  </si>
+  <si>
+    <t>DIACEREIN 30 CAP</t>
+  </si>
+  <si>
+    <t>PEDIAMIL AR MILK 400GM</t>
+  </si>
+  <si>
+    <t>SODIUM BICARBONAT 500 MG 30 TABS</t>
+  </si>
+  <si>
+    <t>HEPTA PANTHENOL CREAM 50 GM</t>
+  </si>
+  <si>
+    <t>BETADERM 0.1% TOPICAL OINT. 15 GM</t>
   </si>
 </sst>
 </file>
@@ -201,7 +216,7 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -398,7 +413,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -666,6 +681,61 @@
         <v>0</v>
       </c>
     </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>73394</v>
+      </c>
+      <c r="B21" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>82119</v>
+      </c>
+      <c r="B22" t="s">
+        <v>39</v>
+      </c>
+      <c r="C22" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>89927</v>
+      </c>
+      <c r="B23" t="s">
+        <v>40</v>
+      </c>
+      <c r="C23" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>85097</v>
+      </c>
+      <c r="B24" t="s">
+        <v>41</v>
+      </c>
+      <c r="C24" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>73931</v>
+      </c>
+      <c r="B25" t="s">
+        <v>42</v>
+      </c>
+      <c r="C25" s="4">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/input/order_items/SMALL_TEST.xlsx
+++ b/data/input/order_items/SMALL_TEST.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\pyreview\PharmaSupplyBot\data\input\order_items\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3883EDC5-9C53-476D-B02F-72A468DA0927}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8AE84D4-FED2-4887-9B34-D3D25E4136DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20010" yWindow="3810" windowWidth="21600" windowHeight="11295" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="54">
   <si>
     <t>كود</t>
   </si>
@@ -154,6 +154,39 @@
   </si>
   <si>
     <t>BETADERM 0.1% TOPICAL OINT. 15 GM</t>
+  </si>
+  <si>
+    <t>ZYRTEC SYRUP 100 ML</t>
+  </si>
+  <si>
+    <t>XILONE SYRUP 100 ml</t>
+  </si>
+  <si>
+    <t>B-FRESH MOUTHWASH MINT 250MLاخضر</t>
+  </si>
+  <si>
+    <t>OPLEX-N PLUS SUPP FOR CHILDREN</t>
+  </si>
+  <si>
+    <t>JACKODAN GEL 60 ML</t>
+  </si>
+  <si>
+    <t>KALOBIN DROPS</t>
+  </si>
+  <si>
+    <t>dr oxygen vitamin d drops</t>
+  </si>
+  <si>
+    <t>CANDICURE1 3 VAG OVULES</t>
+  </si>
+  <si>
+    <t>ALOEKITA ANTI DANDRUFF SHAMPOO</t>
+  </si>
+  <si>
+    <t>GASTROFAIT 1GM TAB</t>
+  </si>
+  <si>
+    <t>IRON-LIPOSOMAL</t>
   </si>
 </sst>
 </file>
@@ -413,7 +446,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J36"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -736,6 +769,70 @@
         <v>0</v>
       </c>
     </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B27" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B29" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B30" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B31" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>92426</v>
+      </c>
+      <c r="B32" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>74057</v>
+      </c>
+      <c r="B33" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>83860</v>
+      </c>
+      <c r="B34" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B35" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B36" t="s">
+        <v>53</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
